--- a/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
+++ b/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSA\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD35782F-1963-4661-A23B-B4662ED8A6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="130-Day Plan" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Progress" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="130-Day Plan" sheetId="1" r:id="rId1"/>
+    <sheet name="Progress" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'130-Day Plan'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'130-Day Plan'!$A$1:$J$131</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -24,12 +38,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -37,7 +51,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Paste the URL of the GitHub Gist containing your solution for this problem, e.g. https://gist.github.com/your-username/abc123def456
+          <t>Paste the URL of the GitHub Gist containing your solution for this problem, e.g. https://gist.github.com/your-username/abc123def456
 One gist per day is enough — include your code plus a short comment on your approach.</t>
         </r>
       </text>
@@ -47,924 +61,925 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="302">
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pattern / Topic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difficulty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LeetCode Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. Time (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why this problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solution Gist Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrays &amp; Basics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The classic first problem — hashmap for O(1) lookup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best Time to Buy and Sell Stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track a running minimum while scanning once</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contains Duplicate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set membership check, O(n) vs O(n^2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum Subarray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduces Kadane's algorithm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move Zeroes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-place array rearrangement, two-pointer flavor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XOR trick — fun 'aha' moment for beginners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Majority Element</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boyer-Moore voting, or simple hashmap counting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus One</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Careful edge-case handling (carry-over digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove Duplicates from Sorted Array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-place modification, sets up two-pointer thinking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merge Sorted Array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merge from the back — a neat trick worth teaching explicitly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two Pointers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid Palindrome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pointers from both ends moving inward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simplest possible two-pointer swap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two Sum II - Input Array Is Sorted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same problem as Day 1, new tool: sorted array + two pointers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove Element</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-place removal, overwrite-in-place pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squares of a Sorted Array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two pointers from outside-in due to negative numbers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sort Colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dutch National Flag — three-pointer partitioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fix one element, two-pointer the rest — very common interview Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Container With Most Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greedy pointer movement based on height comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sliding Window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum Average Subarray I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed-size window — the simplest sliding window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longest Substring Without Repeating Characters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable-size window with a hashset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum Size Subarray Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shrink-the-window-when-valid pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fruit Into Baskets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window with at-most-2-distinct-types constraint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longest Repeating Character Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window + frequency count + a replacement budget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find All Anagrams in a String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed window + character frequency matching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permutation in String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same idea as previous day, different question shape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sliding Window Maximum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stretch problem: monotonic deque — optional, but a great 'aha'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid Anagram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Character frequency counting with a hashmap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Anagrams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use a sorted string (or count tuple) as a hashmap key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top K Frequent Elements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashmap counting + bucket sort or heap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product of Array Except Self</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prefix and suffix products without division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longest Consecutive Sequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashset trick to get O(n) instead of sorting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isomorphic Strings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-way character mapping with two hashmaps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Word Pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same idea as previous day, words instead of characters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ransom Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple frequency-count comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid Parentheses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack basics disguised as a string problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find the Index of the First Occurrence in a String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classic strStr() — brute-force substring search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longest Common Prefix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare characters column by column across strings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse Words in a String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String splitting, trimming, and reassembly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String Compression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-place string building with a write pointer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roman to Integer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashmap + a subtraction special case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integer to Roman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse direction of the previous day's problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zigzag Conversion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulate the zigzag with row buffers — visual, fun to trace on paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linked Lists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse Linked List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE linked-list problem everyone must know cold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merge Two Sorted Lists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dummy-head technique — introduce it here, reuse it forever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linked List Cycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floyd's slow/fast pointer (tortoise and hare)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Middle of the Linked List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same slow/fast pointer trick, different goal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove Linked List Elements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dummy head again, deleting nodes safely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palindrome Linked List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combine: find middle + reverse half + compare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove Nth Node From End of List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two pointers with a fixed gap between them</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add Two Numbers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digit-by-digit addition with carry, linked-list style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reorder List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combine: find middle + reverse half + merge/interleave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copy List with Random Pointer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashmap to map old nodes to new ones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stacks &amp; Queues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design a stack that also tracks its minimum in O(1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement Queue using Stacks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forces real understanding of stack vs queue order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement Stack using Queues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The mirror-image of the previous day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evaluate Reverse Polish Notation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classic stack-based expression evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Temperatures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduces the monotonic stack pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next Greater Element I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same monotonic stack idea, simpler shape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design Circular Queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Array-backed queue with wraparound indices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asteroid Collision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack simulation with directional collision rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The template every later binary-search problem builds on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search Insert Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same template, returns insertion point instead of -1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Bad Version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary search on an API instead of an array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find Peak Element</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary search on a condition, not a sorted value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search in Rotated Sorted Array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decide which half is sorted at each step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find Minimum in Rotated Sorted Array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same rotated-array idea, simpler target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koko Eating Bananas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary search on the ANSWER, not the array — a mindset shift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity To Ship Packages Within D Days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same 'binary search the answer' idea, harder framing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum Depth of Binary Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 'hello world' of recursive tree problems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invert Binary Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple recursive swap — satisfying to visualize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursive structural comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Symmetric Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare a tree against its own mirror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary Tree Level Order Traversal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First real BFS-on-a-tree problem, using a queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balanced Binary Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursion that returns height AND a validity flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diameter of Binary Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track a running answer during a height recursion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Path Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root-to-leaf recursion with a running total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowest Common Ancestor of a Binary Search Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use BST ordering to skip half the tree each step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate Binary Search Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursion with a valid (min, max) range passed down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary Tree Right Side View</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BFS level-order, keep only the last node per level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kth Smallest Element in a BST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-order traversal gives sorted order for free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graphs (BFS/DFS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Islands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE grid-graph problem — DFS/BFS flood fill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flood Fill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same flood-fill idea, simpler framing — good warm-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Area of Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same traversal, now counting cells instead of islands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clone Graph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DFS/BFS + hashmap to avoid cloning nodes twice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Course Schedule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycle detection in a directed graph (topological sort intro)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rotting Oranges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-source BFS — start from many points at once</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacific Atlantic Water Flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DFS from the borders inward, then intersect results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Word Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DFS with backtracking on a grid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surrounded Regions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DFS from the border to mark what should survive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is Graph Bipartite?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-coloring a graph via BFS/DFS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursion &amp; Backtracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subsets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The backtracking template: include/exclude each element</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permutations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backtracking with a 'used' tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combinations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backtracking with a start-index to avoid duplicates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combination Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backtracking where the same number can repeat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Letter Combinations of a Phone Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backtracking over a mapping instead of a single array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate Parentheses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backtracking with two constraints (open/close counts)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palindrome Partitioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backtracking + a palindrome check at each branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-Queens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stretch problem — the 'boss level' of backtracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Programming (1D)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Climbing Stairs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fibonacci in disguise — the gentlest DP intro possible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House Robber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DP with a 'take it or skip it' choice at each step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House Robber II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same idea, now on a circular street</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longest Increasing Subsequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classic O(n^2) DP, can mention O(n log n) as a stretch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coin Change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottom-up DP building up from amount 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum Product Subarray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track running max AND min (negatives flip things)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Word Break</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DP over string prefixes with a dictionary check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decode Ways</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DP with a one-or-two-digit branching choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partition Equal Subset Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subset-sum DP — a very common interview variant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combination Sum IV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DP version of a backtracking problem from Day 91-98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Programming (2D/Grids)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unique Paths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simplest 2D grid DP — count paths, no obstacles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum Path Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same grid, now minimizing a cost instead of counting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triangle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottom-up DP over a triangular grid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longest Common Subsequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The template 2D string-vs-string DP problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximal Square</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2D DP where each cell depends on 3 neighbors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DP reframed as a subset-sum counting problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interleaving String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2D DP tracking two string pointers at once</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit Distance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stretch problem — the 'boss level' of string DP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heaps / Priority Queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kth Largest Element in an Array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min-heap of size k — a reusable trick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Stone Weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max-heap simulation, straightforward warm-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K Closest Points to Origin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same size-k heap trick, different comparison key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top K Frequent Words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heap with a custom tie-breaking comparator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task Scheduler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max-heap + cooldown counting — a fun simulation problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find Median from Data Stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stretch problem — two heaps balancing each other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jump Game</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track the farthest reachable index greedily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gas Station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A greedy proof that feels almost like magic the first time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insert Interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merge a new interval into an already-sorted list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merge Intervals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sort first, then greedily merge overlaps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-overlapping Intervals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greedy interval scheduling by earliest end time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capstone (Mixed Patterns)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRU Cache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ties back to your OOP design checkpoint — hashmap + ordered structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement Trie (Prefix Tree)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A new data structure built entirely from what you already know: nodes + hashmaps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merge k Sorted Lists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand finale: heaps + linked lists + merging, all in one problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130-Day LeetCode Plan — Progress Tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow cells on '130-Day Plan' are for students to fill in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Problems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status: pick from the dropdown (Not Started / In Progress / Done / Skipped).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solution Gist Link: paste your GitHub Gist URL for that day's solution.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example: https://gist.github.com/your-username/abc123def456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skipped</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% Complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difficulty Breakdown</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="303">
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Pattern / Topic</t>
+  </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
+    <t>LeetCode Link</t>
+  </si>
+  <si>
+    <t>Est. Time (min)</t>
+  </si>
+  <si>
+    <t>Why this problem</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Solution Gist Link</t>
+  </si>
+  <si>
+    <t>Arrays &amp; Basics</t>
+  </si>
+  <si>
+    <t>Two Sum</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Open problem</t>
+  </si>
+  <si>
+    <t>The classic first problem — hashmap for O(1) lookup</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Best Time to Buy and Sell Stock</t>
+  </si>
+  <si>
+    <t>Track a running minimum while scanning once</t>
+  </si>
+  <si>
+    <t>Contains Duplicate</t>
+  </si>
+  <si>
+    <t>Set membership check, O(n) vs O(n^2)</t>
+  </si>
+  <si>
+    <t>Maximum Subarray</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Introduces Kadane's algorithm</t>
+  </si>
+  <si>
+    <t>Move Zeroes</t>
+  </si>
+  <si>
+    <t>In-place array rearrangement, two-pointer flavor</t>
+  </si>
+  <si>
+    <t>Single Number</t>
+  </si>
+  <si>
+    <t>XOR trick — fun 'aha' moment for beginners</t>
+  </si>
+  <si>
+    <t>Majority Element</t>
+  </si>
+  <si>
+    <t>Boyer-Moore voting, or simple hashmap counting</t>
+  </si>
+  <si>
+    <t>Plus One</t>
+  </si>
+  <si>
+    <t>Careful edge-case handling (carry-over digits)</t>
+  </si>
+  <si>
+    <t>Remove Duplicates from Sorted Array</t>
+  </si>
+  <si>
+    <t>In-place modification, sets up two-pointer thinking</t>
+  </si>
+  <si>
+    <t>Merge Sorted Array</t>
+  </si>
+  <si>
+    <t>Merge from the back — a neat trick worth teaching explicitly</t>
+  </si>
+  <si>
+    <t>Two Pointers</t>
+  </si>
+  <si>
+    <t>Valid Palindrome</t>
+  </si>
+  <si>
+    <t>Pointers from both ends moving inward</t>
+  </si>
+  <si>
+    <t>Reverse String</t>
+  </si>
+  <si>
+    <t>Simplest possible two-pointer swap</t>
+  </si>
+  <si>
+    <t>Two Sum II - Input Array Is Sorted</t>
+  </si>
+  <si>
+    <t>Same problem as Day 1, new tool: sorted array + two pointers</t>
+  </si>
+  <si>
+    <t>Remove Element</t>
+  </si>
+  <si>
+    <t>In-place removal, overwrite-in-place pattern</t>
+  </si>
+  <si>
+    <t>Squares of a Sorted Array</t>
+  </si>
+  <si>
+    <t>Two pointers from outside-in due to negative numbers</t>
+  </si>
+  <si>
+    <t>Sort Colors</t>
+  </si>
+  <si>
+    <t>Dutch National Flag — three-pointer partitioning</t>
+  </si>
+  <si>
+    <t>3Sum</t>
+  </si>
+  <si>
+    <t>Fix one element, two-pointer the rest — very common interview Q</t>
+  </si>
+  <si>
+    <t>Container With Most Water</t>
+  </si>
+  <si>
+    <t>Greedy pointer movement based on height comparison</t>
+  </si>
+  <si>
+    <t>Sliding Window</t>
+  </si>
+  <si>
+    <t>Maximum Average Subarray I</t>
+  </si>
+  <si>
+    <t>Fixed-size window — the simplest sliding window</t>
+  </si>
+  <si>
+    <t>Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>Variable-size window with a hashset</t>
+  </si>
+  <si>
+    <t>Minimum Size Subarray Sum</t>
+  </si>
+  <si>
+    <t>Shrink-the-window-when-valid pattern</t>
+  </si>
+  <si>
+    <t>Fruit Into Baskets</t>
+  </si>
+  <si>
+    <t>Window with at-most-2-distinct-types constraint</t>
+  </si>
+  <si>
+    <t>Longest Repeating Character Replacement</t>
+  </si>
+  <si>
+    <t>Window + frequency count + a replacement budget</t>
+  </si>
+  <si>
+    <t>Find All Anagrams in a String</t>
+  </si>
+  <si>
+    <t>Fixed window + character frequency matching</t>
+  </si>
+  <si>
+    <t>Permutation in String</t>
+  </si>
+  <si>
+    <t>Same idea as previous day, different question shape</t>
+  </si>
+  <si>
+    <t>Sliding Window Maximum</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t>Stretch problem: monotonic deque — optional, but a great 'aha'</t>
+  </si>
+  <si>
+    <t>Hashing</t>
+  </si>
+  <si>
+    <t>Valid Anagram</t>
+  </si>
+  <si>
+    <t>Character frequency counting with a hashmap</t>
+  </si>
+  <si>
+    <t>Group Anagrams</t>
+  </si>
+  <si>
+    <t>Use a sorted string (or count tuple) as a hashmap key</t>
+  </si>
+  <si>
+    <t>Top K Frequent Elements</t>
+  </si>
+  <si>
+    <t>Hashmap counting + bucket sort or heap</t>
+  </si>
+  <si>
+    <t>Product of Array Except Self</t>
+  </si>
+  <si>
+    <t>Prefix and suffix products without division</t>
+  </si>
+  <si>
+    <t>Longest Consecutive Sequence</t>
+  </si>
+  <si>
+    <t>Hashset trick to get O(n) instead of sorting</t>
+  </si>
+  <si>
+    <t>Isomorphic Strings</t>
+  </si>
+  <si>
+    <t>Two-way character mapping with two hashmaps</t>
+  </si>
+  <si>
+    <t>Word Pattern</t>
+  </si>
+  <si>
+    <t>Same idea as previous day, words instead of characters</t>
+  </si>
+  <si>
+    <t>Ransom Note</t>
+  </si>
+  <si>
+    <t>Simple frequency-count comparison</t>
+  </si>
+  <si>
+    <t>Strings</t>
+  </si>
+  <si>
+    <t>Valid Parentheses</t>
+  </si>
+  <si>
+    <t>Stack basics disguised as a string problem</t>
+  </si>
+  <si>
+    <t>Find the Index of the First Occurrence in a String</t>
+  </si>
+  <si>
+    <t>Classic strStr() — brute-force substring search</t>
+  </si>
+  <si>
+    <t>Longest Common Prefix</t>
+  </si>
+  <si>
+    <t>Compare characters column by column across strings</t>
+  </si>
+  <si>
+    <t>Reverse Words in a String</t>
+  </si>
+  <si>
+    <t>String splitting, trimming, and reassembly</t>
+  </si>
+  <si>
+    <t>String Compression</t>
+  </si>
+  <si>
+    <t>In-place string building with a write pointer</t>
+  </si>
+  <si>
+    <t>Roman to Integer</t>
+  </si>
+  <si>
+    <t>Hashmap + a subtraction special case</t>
+  </si>
+  <si>
+    <t>Integer to Roman</t>
+  </si>
+  <si>
+    <t>Reverse direction of the previous day's problem</t>
+  </si>
+  <si>
+    <t>Zigzag Conversion</t>
+  </si>
+  <si>
+    <t>Simulate the zigzag with row buffers — visual, fun to trace on paper</t>
+  </si>
+  <si>
+    <t>Linked Lists</t>
+  </si>
+  <si>
+    <t>Reverse Linked List</t>
+  </si>
+  <si>
+    <t>THE linked-list problem everyone must know cold</t>
+  </si>
+  <si>
+    <t>Merge Two Sorted Lists</t>
+  </si>
+  <si>
+    <t>Dummy-head technique — introduce it here, reuse it forever</t>
+  </si>
+  <si>
+    <t>Linked List Cycle</t>
+  </si>
+  <si>
+    <t>Floyd's slow/fast pointer (tortoise and hare)</t>
+  </si>
+  <si>
+    <t>Middle of the Linked List</t>
+  </si>
+  <si>
+    <t>Same slow/fast pointer trick, different goal</t>
+  </si>
+  <si>
+    <t>Remove Linked List Elements</t>
+  </si>
+  <si>
+    <t>Dummy head again, deleting nodes safely</t>
+  </si>
+  <si>
+    <t>Palindrome Linked List</t>
+  </si>
+  <si>
+    <t>Combine: find middle + reverse half + compare</t>
+  </si>
+  <si>
+    <t>Remove Nth Node From End of List</t>
+  </si>
+  <si>
+    <t>Two pointers with a fixed gap between them</t>
+  </si>
+  <si>
+    <t>Add Two Numbers</t>
+  </si>
+  <si>
+    <t>Digit-by-digit addition with carry, linked-list style</t>
+  </si>
+  <si>
+    <t>Reorder List</t>
+  </si>
+  <si>
+    <t>Combine: find middle + reverse half + merge/interleave</t>
+  </si>
+  <si>
+    <t>Copy List with Random Pointer</t>
+  </si>
+  <si>
+    <t>Hashmap to map old nodes to new ones</t>
+  </si>
+  <si>
+    <t>Stacks &amp; Queues</t>
+  </si>
+  <si>
+    <t>Min Stack</t>
+  </si>
+  <si>
+    <t>Design a stack that also tracks its minimum in O(1)</t>
+  </si>
+  <si>
+    <t>Implement Queue using Stacks</t>
+  </si>
+  <si>
+    <t>Forces real understanding of stack vs queue order</t>
+  </si>
+  <si>
+    <t>Implement Stack using Queues</t>
+  </si>
+  <si>
+    <t>The mirror-image of the previous day</t>
+  </si>
+  <si>
+    <t>Evaluate Reverse Polish Notation</t>
+  </si>
+  <si>
+    <t>Classic stack-based expression evaluation</t>
+  </si>
+  <si>
+    <t>Daily Temperatures</t>
+  </si>
+  <si>
+    <t>Introduces the monotonic stack pattern</t>
+  </si>
+  <si>
+    <t>Next Greater Element I</t>
+  </si>
+  <si>
+    <t>Same monotonic stack idea, simpler shape</t>
+  </si>
+  <si>
+    <t>Design Circular Queue</t>
+  </si>
+  <si>
+    <t>Array-backed queue with wraparound indices</t>
+  </si>
+  <si>
+    <t>Asteroid Collision</t>
+  </si>
+  <si>
+    <t>Stack simulation with directional collision rules</t>
+  </si>
+  <si>
+    <t>Binary Search</t>
+  </si>
+  <si>
+    <t>The template every later binary-search problem builds on</t>
+  </si>
+  <si>
+    <t>Search Insert Position</t>
+  </si>
+  <si>
+    <t>Same template, returns insertion point instead of -1</t>
+  </si>
+  <si>
+    <t>First Bad Version</t>
+  </si>
+  <si>
+    <t>Binary search on an API instead of an array</t>
+  </si>
+  <si>
+    <t>Find Peak Element</t>
+  </si>
+  <si>
+    <t>Binary search on a condition, not a sorted value</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>Decide which half is sorted at each step</t>
+  </si>
+  <si>
+    <t>Find Minimum in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>Same rotated-array idea, simpler target</t>
+  </si>
+  <si>
+    <t>Koko Eating Bananas</t>
+  </si>
+  <si>
+    <t>Binary search on the ANSWER, not the array — a mindset shift</t>
+  </si>
+  <si>
+    <t>Capacity To Ship Packages Within D Days</t>
+  </si>
+  <si>
+    <t>Same 'binary search the answer' idea, harder framing</t>
+  </si>
+  <si>
+    <t>Trees</t>
+  </si>
+  <si>
+    <t>Maximum Depth of Binary Tree</t>
+  </si>
+  <si>
+    <t>The 'hello world' of recursive tree problems</t>
+  </si>
+  <si>
+    <t>Invert Binary Tree</t>
+  </si>
+  <si>
+    <t>Simple recursive swap — satisfying to visualize</t>
+  </si>
+  <si>
+    <t>Same Tree</t>
+  </si>
+  <si>
+    <t>Recursive structural comparison</t>
+  </si>
+  <si>
+    <t>Symmetric Tree</t>
+  </si>
+  <si>
+    <t>Compare a tree against its own mirror</t>
+  </si>
+  <si>
+    <t>Binary Tree Level Order Traversal</t>
+  </si>
+  <si>
+    <t>First real BFS-on-a-tree problem, using a queue</t>
+  </si>
+  <si>
+    <t>Balanced Binary Tree</t>
+  </si>
+  <si>
+    <t>Recursion that returns height AND a validity flag</t>
+  </si>
+  <si>
+    <t>Diameter of Binary Tree</t>
+  </si>
+  <si>
+    <t>Track a running answer during a height recursion</t>
+  </si>
+  <si>
+    <t>Path Sum</t>
+  </si>
+  <si>
+    <t>Root-to-leaf recursion with a running total</t>
+  </si>
+  <si>
+    <t>Lowest Common Ancestor of a Binary Search Tree</t>
+  </si>
+  <si>
+    <t>Use BST ordering to skip half the tree each step</t>
+  </si>
+  <si>
+    <t>Validate Binary Search Tree</t>
+  </si>
+  <si>
+    <t>Recursion with a valid (min, max) range passed down</t>
+  </si>
+  <si>
+    <t>Binary Tree Right Side View</t>
+  </si>
+  <si>
+    <t>BFS level-order, keep only the last node per level</t>
+  </si>
+  <si>
+    <t>Kth Smallest Element in a BST</t>
+  </si>
+  <si>
+    <t>In-order traversal gives sorted order for free</t>
+  </si>
+  <si>
+    <t>Graphs (BFS/DFS)</t>
+  </si>
+  <si>
+    <t>Number of Islands</t>
+  </si>
+  <si>
+    <t>THE grid-graph problem — DFS/BFS flood fill</t>
+  </si>
+  <si>
+    <t>Flood Fill</t>
+  </si>
+  <si>
+    <t>Same flood-fill idea, simpler framing — good warm-up</t>
+  </si>
+  <si>
+    <t>Max Area of Island</t>
+  </si>
+  <si>
+    <t>Same traversal, now counting cells instead of islands</t>
+  </si>
+  <si>
+    <t>Clone Graph</t>
+  </si>
+  <si>
+    <t>DFS/BFS + hashmap to avoid cloning nodes twice</t>
+  </si>
+  <si>
+    <t>Course Schedule</t>
+  </si>
+  <si>
+    <t>Cycle detection in a directed graph (topological sort intro)</t>
+  </si>
+  <si>
+    <t>Rotting Oranges</t>
+  </si>
+  <si>
+    <t>Multi-source BFS — start from many points at once</t>
+  </si>
+  <si>
+    <t>Pacific Atlantic Water Flow</t>
+  </si>
+  <si>
+    <t>DFS from the borders inward, then intersect results</t>
+  </si>
+  <si>
+    <t>Word Search</t>
+  </si>
+  <si>
+    <t>DFS with backtracking on a grid</t>
+  </si>
+  <si>
+    <t>Surrounded Regions</t>
+  </si>
+  <si>
+    <t>DFS from the border to mark what should survive</t>
+  </si>
+  <si>
+    <t>Is Graph Bipartite?</t>
+  </si>
+  <si>
+    <t>Two-coloring a graph via BFS/DFS</t>
+  </si>
+  <si>
+    <t>Recursion &amp; Backtracking</t>
+  </si>
+  <si>
+    <t>Subsets</t>
+  </si>
+  <si>
+    <t>The backtracking template: include/exclude each element</t>
+  </si>
+  <si>
+    <t>Permutations</t>
+  </si>
+  <si>
+    <t>Backtracking with a 'used' tracker</t>
+  </si>
+  <si>
+    <t>Combinations</t>
+  </si>
+  <si>
+    <t>Backtracking with a start-index to avoid duplicates</t>
+  </si>
+  <si>
+    <t>Combination Sum</t>
+  </si>
+  <si>
+    <t>Backtracking where the same number can repeat</t>
+  </si>
+  <si>
+    <t>Letter Combinations of a Phone Number</t>
+  </si>
+  <si>
+    <t>Backtracking over a mapping instead of a single array</t>
+  </si>
+  <si>
+    <t>Generate Parentheses</t>
+  </si>
+  <si>
+    <t>Backtracking with two constraints (open/close counts)</t>
+  </si>
+  <si>
+    <t>Palindrome Partitioning</t>
+  </si>
+  <si>
+    <t>Backtracking + a palindrome check at each branch</t>
+  </si>
+  <si>
+    <t>N-Queens</t>
+  </si>
+  <si>
+    <t>Stretch problem — the 'boss level' of backtracking</t>
+  </si>
+  <si>
+    <t>Dynamic Programming (1D)</t>
+  </si>
+  <si>
+    <t>Climbing Stairs</t>
+  </si>
+  <si>
+    <t>Fibonacci in disguise — the gentlest DP intro possible</t>
+  </si>
+  <si>
+    <t>House Robber</t>
+  </si>
+  <si>
+    <t>DP with a 'take it or skip it' choice at each step</t>
+  </si>
+  <si>
+    <t>House Robber II</t>
+  </si>
+  <si>
+    <t>Same idea, now on a circular street</t>
+  </si>
+  <si>
+    <t>Longest Increasing Subsequence</t>
+  </si>
+  <si>
+    <t>Classic O(n^2) DP, can mention O(n log n) as a stretch</t>
+  </si>
+  <si>
+    <t>Coin Change</t>
+  </si>
+  <si>
+    <t>Bottom-up DP building up from amount 0</t>
+  </si>
+  <si>
+    <t>Maximum Product Subarray</t>
+  </si>
+  <si>
+    <t>Track running max AND min (negatives flip things)</t>
+  </si>
+  <si>
+    <t>Word Break</t>
+  </si>
+  <si>
+    <t>DP over string prefixes with a dictionary check</t>
+  </si>
+  <si>
+    <t>Decode Ways</t>
+  </si>
+  <si>
+    <t>DP with a one-or-two-digit branching choice</t>
+  </si>
+  <si>
+    <t>Partition Equal Subset Sum</t>
+  </si>
+  <si>
+    <t>Subset-sum DP — a very common interview variant</t>
+  </si>
+  <si>
+    <t>Combination Sum IV</t>
+  </si>
+  <si>
+    <t>DP version of a backtracking problem from Day 91-98</t>
+  </si>
+  <si>
+    <t>Dynamic Programming (2D/Grids)</t>
+  </si>
+  <si>
+    <t>Unique Paths</t>
+  </si>
+  <si>
+    <t>Simplest 2D grid DP — count paths, no obstacles</t>
+  </si>
+  <si>
+    <t>Minimum Path Sum</t>
+  </si>
+  <si>
+    <t>Same grid, now minimizing a cost instead of counting</t>
+  </si>
+  <si>
+    <t>Triangle</t>
+  </si>
+  <si>
+    <t>Bottom-up DP over a triangular grid</t>
+  </si>
+  <si>
+    <t>Longest Common Subsequence</t>
+  </si>
+  <si>
+    <t>The template 2D string-vs-string DP problem</t>
+  </si>
+  <si>
+    <t>Maximal Square</t>
+  </si>
+  <si>
+    <t>2D DP where each cell depends on 3 neighbors</t>
+  </si>
+  <si>
+    <t>Target Sum</t>
+  </si>
+  <si>
+    <t>DP reframed as a subset-sum counting problem</t>
+  </si>
+  <si>
+    <t>Interleaving String</t>
+  </si>
+  <si>
+    <t>2D DP tracking two string pointers at once</t>
+  </si>
+  <si>
+    <t>Edit Distance</t>
+  </si>
+  <si>
+    <t>Stretch problem — the 'boss level' of string DP</t>
+  </si>
+  <si>
+    <t>Heaps / Priority Queue</t>
+  </si>
+  <si>
+    <t>Kth Largest Element in an Array</t>
+  </si>
+  <si>
+    <t>Min-heap of size k — a reusable trick</t>
+  </si>
+  <si>
+    <t>Last Stone Weight</t>
+  </si>
+  <si>
+    <t>Max-heap simulation, straightforward warm-up</t>
+  </si>
+  <si>
+    <t>K Closest Points to Origin</t>
+  </si>
+  <si>
+    <t>Same size-k heap trick, different comparison key</t>
+  </si>
+  <si>
+    <t>Top K Frequent Words</t>
+  </si>
+  <si>
+    <t>Heap with a custom tie-breaking comparator</t>
+  </si>
+  <si>
+    <t>Task Scheduler</t>
+  </si>
+  <si>
+    <t>Max-heap + cooldown counting — a fun simulation problem</t>
+  </si>
+  <si>
+    <t>Find Median from Data Stream</t>
+  </si>
+  <si>
+    <t>Stretch problem — two heaps balancing each other</t>
+  </si>
+  <si>
+    <t>Greedy</t>
+  </si>
+  <si>
+    <t>Jump Game</t>
+  </si>
+  <si>
+    <t>Track the farthest reachable index greedily</t>
+  </si>
+  <si>
+    <t>Gas Station</t>
+  </si>
+  <si>
+    <t>A greedy proof that feels almost like magic the first time</t>
+  </si>
+  <si>
+    <t>Insert Interval</t>
+  </si>
+  <si>
+    <t>Merge a new interval into an already-sorted list</t>
+  </si>
+  <si>
+    <t>Merge Intervals</t>
+  </si>
+  <si>
+    <t>Sort first, then greedily merge overlaps</t>
+  </si>
+  <si>
+    <t>Non-overlapping Intervals</t>
+  </si>
+  <si>
+    <t>Greedy interval scheduling by earliest end time</t>
+  </si>
+  <si>
+    <t>Capstone (Mixed Patterns)</t>
+  </si>
+  <si>
+    <t>LRU Cache</t>
+  </si>
+  <si>
+    <t>Ties back to your OOP design checkpoint — hashmap + ordered structure</t>
+  </si>
+  <si>
+    <t>Implement Trie (Prefix Tree)</t>
+  </si>
+  <si>
+    <t>A new data structure built entirely from what you already know: nodes + hashmaps</t>
+  </si>
+  <si>
+    <t>Merge k Sorted Lists</t>
+  </si>
+  <si>
+    <t>Grand finale: heaps + linked lists + merging, all in one problem</t>
+  </si>
+  <si>
+    <t>130-Day LeetCode Plan — Progress Tracker</t>
+  </si>
+  <si>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>Yellow cells on '130-Day Plan' are for students to fill in.</t>
+  </si>
+  <si>
+    <t>Total Problems</t>
+  </si>
+  <si>
+    <t>Status: pick from the dropdown (Not Started / In Progress / Done / Skipped).</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Solution Gist Link: paste your GitHub Gist URL for that day's solution.</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Example: https://gist.github.com/your-username/abc123def456</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>% Complete</t>
+  </si>
+  <si>
+    <t>Difficulty Breakdown</t>
+  </si>
+  <si>
+    <t>completed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -973,61 +988,40 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1036,30 +1030,26 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1102,14 +1092,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1125,194 +1115,44 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF2F3B52"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF006100"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9C0006"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9C6500"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0563C1"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1371,51 +1211,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF2F3B52"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1423,12 +1275,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1457,7 +1309,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1478,7 +1330,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1529,7 +1381,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1547,35 +1399,34 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J131"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="34"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1607,8 +1458,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1623,20 +1474,20 @@
       <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>15</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1651,20 +1502,20 @@
       <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="2">
         <v>15</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1679,20 +1530,20 @@
       <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="2">
         <v>10</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1707,7 +1558,7 @@
       <c r="E5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="2">
         <v>20</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -1719,8 +1570,8 @@
       <c r="I5" s="3"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1735,20 +1586,20 @@
       <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="2">
         <v>15</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1763,20 +1614,20 @@
       <c r="E7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="2">
         <v>10</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1791,7 +1642,7 @@
       <c r="E8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="2">
         <v>15</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -1803,8 +1654,8 @@
       <c r="I8" s="3"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1819,7 +1670,7 @@
       <c r="E9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="2">
         <v>10</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1831,8 +1682,8 @@
       <c r="I9" s="3"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1847,7 +1698,7 @@
       <c r="E10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="2">
         <v>15</v>
       </c>
       <c r="G10" s="6" t="s">
@@ -1859,8 +1710,8 @@
       <c r="I10" s="3"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1875,7 +1726,7 @@
       <c r="E11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="2">
         <v>15</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -1887,8 +1738,8 @@
       <c r="I11" s="3"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1903,7 +1754,7 @@
       <c r="E12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="2">
         <v>15</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -1915,8 +1766,8 @@
       <c r="I12" s="3"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1931,7 +1782,7 @@
       <c r="E13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="2">
         <v>10</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -1943,8 +1794,8 @@
       <c r="I13" s="3"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1959,7 +1810,7 @@
       <c r="E14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="2">
         <v>15</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -1971,8 +1822,8 @@
       <c r="I14" s="3"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1987,7 +1838,7 @@
       <c r="E15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="2">
         <v>10</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -1999,8 +1850,8 @@
       <c r="I15" s="3"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2015,7 +1866,7 @@
       <c r="E16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="2">
         <v>15</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -2027,8 +1878,8 @@
       <c r="I16" s="3"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2043,7 +1894,7 @@
       <c r="E17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="2">
         <v>20</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -2055,8 +1906,8 @@
       <c r="I17" s="3"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2071,7 +1922,7 @@
       <c r="E18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="2">
         <v>25</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -2083,8 +1934,8 @@
       <c r="I18" s="3"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+    <row r="19" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -2099,7 +1950,7 @@
       <c r="E19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="2">
         <v>20</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -2111,8 +1962,8 @@
       <c r="I19" s="3"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -2127,7 +1978,7 @@
       <c r="E20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="2">
         <v>15</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -2139,8 +1990,8 @@
       <c r="I20" s="3"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -2155,7 +2006,7 @@
       <c r="E21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="2">
         <v>20</v>
       </c>
       <c r="G21" s="6" t="s">
@@ -2167,8 +2018,8 @@
       <c r="I21" s="3"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -2183,7 +2034,7 @@
       <c r="E22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="2">
         <v>20</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -2195,8 +2046,8 @@
       <c r="I22" s="3"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -2211,7 +2062,7 @@
       <c r="E23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="2">
         <v>20</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -2223,8 +2074,8 @@
       <c r="I23" s="3"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -2239,7 +2090,7 @@
       <c r="E24" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="2">
         <v>25</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -2251,8 +2102,8 @@
       <c r="I24" s="3"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -2267,7 +2118,7 @@
       <c r="E25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="2">
         <v>20</v>
       </c>
       <c r="G25" s="6" t="s">
@@ -2279,8 +2130,8 @@
       <c r="I25" s="3"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -2295,7 +2146,7 @@
       <c r="E26" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="2">
         <v>20</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -2307,8 +2158,8 @@
       <c r="I26" s="3"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -2323,7 +2174,7 @@
       <c r="E27" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="2">
         <v>30</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -2335,8 +2186,8 @@
       <c r="I27" s="3"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -2351,7 +2202,7 @@
       <c r="E28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="2">
         <v>10</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -2363,8 +2214,8 @@
       <c r="I28" s="3"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="n">
+    <row r="29" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -2379,7 +2230,7 @@
       <c r="E29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="2">
         <v>20</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -2391,8 +2242,8 @@
       <c r="I29" s="3"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -2407,7 +2258,7 @@
       <c r="E30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="2">
         <v>20</v>
       </c>
       <c r="G30" s="6" t="s">
@@ -2419,8 +2270,8 @@
       <c r="I30" s="3"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="n">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -2435,7 +2286,7 @@
       <c r="E31" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="2">
         <v>20</v>
       </c>
       <c r="G31" s="6" t="s">
@@ -2447,8 +2298,8 @@
       <c r="I31" s="3"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -2463,7 +2314,7 @@
       <c r="E32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="2">
         <v>25</v>
       </c>
       <c r="G32" s="6" t="s">
@@ -2475,8 +2326,8 @@
       <c r="I32" s="3"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="n">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -2491,7 +2342,7 @@
       <c r="E33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="2">
         <v>15</v>
       </c>
       <c r="G33" s="6" t="s">
@@ -2503,8 +2354,8 @@
       <c r="I33" s="3"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -2519,7 +2370,7 @@
       <c r="E34" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="2">
         <v>15</v>
       </c>
       <c r="G34" s="6" t="s">
@@ -2531,8 +2382,8 @@
       <c r="I34" s="3"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="n">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -2547,7 +2398,7 @@
       <c r="E35" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="6" t="s">
@@ -2559,8 +2410,8 @@
       <c r="I35" s="3"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -2575,7 +2426,7 @@
       <c r="E36" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="2">
         <v>15</v>
       </c>
       <c r="G36" s="6" t="s">
@@ -2587,8 +2438,8 @@
       <c r="I36" s="3"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="n">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -2603,7 +2454,7 @@
       <c r="E37" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="2">
         <v>15</v>
       </c>
       <c r="G37" s="6" t="s">
@@ -2615,8 +2466,8 @@
       <c r="I37" s="3"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -2631,7 +2482,7 @@
       <c r="E38" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="2">
         <v>15</v>
       </c>
       <c r="G38" s="6" t="s">
@@ -2643,8 +2494,8 @@
       <c r="I38" s="3"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="n">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -2659,7 +2510,7 @@
       <c r="E39" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="2">
         <v>20</v>
       </c>
       <c r="G39" s="6" t="s">
@@ -2671,8 +2522,8 @@
       <c r="I39" s="3"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -2687,7 +2538,7 @@
       <c r="E40" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" s="2">
         <v>20</v>
       </c>
       <c r="G40" s="6" t="s">
@@ -2699,8 +2550,8 @@
       <c r="I40" s="3"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="n">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -2715,7 +2566,7 @@
       <c r="E41" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="2">
         <v>15</v>
       </c>
       <c r="G41" s="6" t="s">
@@ -2727,8 +2578,8 @@
       <c r="I41" s="3"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -2743,7 +2594,7 @@
       <c r="E42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="6" t="s">
@@ -2755,8 +2606,8 @@
       <c r="I42" s="3"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="n">
+    <row r="43" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -2771,7 +2622,7 @@
       <c r="E43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" s="2">
         <v>20</v>
       </c>
       <c r="G43" s="6" t="s">
@@ -2783,8 +2634,8 @@
       <c r="I43" s="3"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -2799,7 +2650,7 @@
       <c r="E44" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" s="2">
         <v>15</v>
       </c>
       <c r="G44" s="6" t="s">
@@ -2811,8 +2662,8 @@
       <c r="I44" s="3"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="n">
+    <row r="45" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -2827,7 +2678,7 @@
       <c r="E45" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" s="2">
         <v>15</v>
       </c>
       <c r="G45" s="6" t="s">
@@ -2839,8 +2690,8 @@
       <c r="I45" s="3"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -2855,7 +2706,7 @@
       <c r="E46" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" s="2">
         <v>15</v>
       </c>
       <c r="G46" s="6" t="s">
@@ -2867,8 +2718,8 @@
       <c r="I46" s="3"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="n">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -2883,7 +2734,7 @@
       <c r="E47" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="6" t="s">
@@ -2895,8 +2746,8 @@
       <c r="I47" s="3"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -2911,7 +2762,7 @@
       <c r="E48" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="2">
         <v>15</v>
       </c>
       <c r="G48" s="6" t="s">
@@ -2923,8 +2774,8 @@
       <c r="I48" s="3"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="n">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -2939,7 +2790,7 @@
       <c r="E49" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" s="2">
         <v>20</v>
       </c>
       <c r="G49" s="6" t="s">
@@ -2951,8 +2802,8 @@
       <c r="I49" s="3"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="n">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -2967,7 +2818,7 @@
       <c r="E50" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="2">
         <v>20</v>
       </c>
       <c r="G50" s="6" t="s">
@@ -2979,8 +2830,8 @@
       <c r="I50" s="3"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="n">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -2995,7 +2846,7 @@
       <c r="E51" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" s="2">
         <v>25</v>
       </c>
       <c r="G51" s="6" t="s">
@@ -3007,8 +2858,8 @@
       <c r="I51" s="3"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="n">
+    <row r="52" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -3023,7 +2874,7 @@
       <c r="E52" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="2">
         <v>25</v>
       </c>
       <c r="G52" s="6" t="s">
@@ -3035,8 +2886,8 @@
       <c r="I52" s="3"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="n">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -3051,7 +2902,7 @@
       <c r="E53" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="2">
         <v>25</v>
       </c>
       <c r="G53" s="6" t="s">
@@ -3063,8 +2914,8 @@
       <c r="I53" s="3"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="n">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -3079,7 +2930,7 @@
       <c r="E54" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" s="2">
         <v>20</v>
       </c>
       <c r="G54" s="6" t="s">
@@ -3091,8 +2942,8 @@
       <c r="I54" s="3"/>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="n">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -3107,7 +2958,7 @@
       <c r="E55" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="2">
         <v>15</v>
       </c>
       <c r="G55" s="6" t="s">
@@ -3119,8 +2970,8 @@
       <c r="I55" s="3"/>
       <c r="J55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="n">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -3135,7 +2986,7 @@
       <c r="E56" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="2">
         <v>15</v>
       </c>
       <c r="G56" s="6" t="s">
@@ -3147,8 +2998,8 @@
       <c r="I56" s="3"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="n">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -3163,7 +3014,7 @@
       <c r="E57" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="2">
         <v>20</v>
       </c>
       <c r="G57" s="6" t="s">
@@ -3175,8 +3026,8 @@
       <c r="I57" s="3"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="n">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -3191,7 +3042,7 @@
       <c r="E58" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F58" s="2">
         <v>20</v>
       </c>
       <c r="G58" s="6" t="s">
@@ -3203,8 +3054,8 @@
       <c r="I58" s="3"/>
       <c r="J58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="n">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -3219,7 +3070,7 @@
       <c r="E59" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" s="2">
         <v>15</v>
       </c>
       <c r="G59" s="6" t="s">
@@ -3231,8 +3082,8 @@
       <c r="I59" s="3"/>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="n">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -3247,7 +3098,7 @@
       <c r="E60" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F60" s="2">
         <v>20</v>
       </c>
       <c r="G60" s="6" t="s">
@@ -3259,8 +3110,8 @@
       <c r="I60" s="3"/>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="n">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -3275,7 +3126,7 @@
       <c r="E61" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" s="2">
         <v>20</v>
       </c>
       <c r="G61" s="6" t="s">
@@ -3287,8 +3138,8 @@
       <c r="I61" s="3"/>
       <c r="J61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="n">
+    <row r="62" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -3303,7 +3154,7 @@
       <c r="E62" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="2">
         <v>10</v>
       </c>
       <c r="G62" s="6" t="s">
@@ -3315,8 +3166,8 @@
       <c r="I62" s="3"/>
       <c r="J62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="n">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -3331,7 +3182,7 @@
       <c r="E63" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" s="2">
         <v>10</v>
       </c>
       <c r="G63" s="6" t="s">
@@ -3343,8 +3194,8 @@
       <c r="I63" s="3"/>
       <c r="J63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="n">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -3359,7 +3210,7 @@
       <c r="E64" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" s="2">
         <v>15</v>
       </c>
       <c r="G64" s="6" t="s">
@@ -3371,8 +3222,8 @@
       <c r="I64" s="3"/>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="n">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -3387,7 +3238,7 @@
       <c r="E65" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="2">
         <v>20</v>
       </c>
       <c r="G65" s="6" t="s">
@@ -3399,8 +3250,8 @@
       <c r="I65" s="3"/>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="n">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -3415,7 +3266,7 @@
       <c r="E66" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="2">
         <v>25</v>
       </c>
       <c r="G66" s="6" t="s">
@@ -3427,8 +3278,8 @@
       <c r="I66" s="3"/>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="n">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -3443,7 +3294,7 @@
       <c r="E67" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F67" s="2">
         <v>20</v>
       </c>
       <c r="G67" s="6" t="s">
@@ -3455,8 +3306,8 @@
       <c r="I67" s="3"/>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="n">
+    <row r="68" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -3471,7 +3322,7 @@
       <c r="E68" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F68" s="2">
         <v>20</v>
       </c>
       <c r="G68" s="6" t="s">
@@ -3483,8 +3334,8 @@
       <c r="I68" s="3"/>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="n">
+    <row r="69" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -3499,7 +3350,7 @@
       <c r="E69" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F69" s="2">
         <v>25</v>
       </c>
       <c r="G69" s="6" t="s">
@@ -3511,8 +3362,8 @@
       <c r="I69" s="3"/>
       <c r="J69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="n">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -3527,7 +3378,7 @@
       <c r="E70" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="F70" s="2">
         <v>10</v>
       </c>
       <c r="G70" s="6" t="s">
@@ -3539,8 +3390,8 @@
       <c r="I70" s="3"/>
       <c r="J70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="n">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -3555,7 +3406,7 @@
       <c r="E71" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="F71" s="2">
         <v>10</v>
       </c>
       <c r="G71" s="6" t="s">
@@ -3567,8 +3418,8 @@
       <c r="I71" s="3"/>
       <c r="J71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="n">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -3583,7 +3434,7 @@
       <c r="E72" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="F72" s="2">
         <v>10</v>
       </c>
       <c r="G72" s="6" t="s">
@@ -3595,8 +3446,8 @@
       <c r="I72" s="3"/>
       <c r="J72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="n">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -3611,7 +3462,7 @@
       <c r="E73" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F73" s="2">
         <v>15</v>
       </c>
       <c r="G73" s="6" t="s">
@@ -3623,8 +3474,8 @@
       <c r="I73" s="3"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="n">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -3639,7 +3490,7 @@
       <c r="E74" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F74" s="2">
         <v>20</v>
       </c>
       <c r="G74" s="6" t="s">
@@ -3651,8 +3502,8 @@
       <c r="I74" s="3"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="n">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A75" s="2">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -3667,7 +3518,7 @@
       <c r="E75" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="F75" s="2">
         <v>15</v>
       </c>
       <c r="G75" s="6" t="s">
@@ -3679,8 +3530,8 @@
       <c r="I75" s="3"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="n">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -3695,7 +3546,7 @@
       <c r="E76" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="2">
         <v>20</v>
       </c>
       <c r="G76" s="6" t="s">
@@ -3707,8 +3558,8 @@
       <c r="I76" s="3"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="n">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A77" s="2">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -3723,7 +3574,7 @@
       <c r="E77" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="2">
         <v>15</v>
       </c>
       <c r="G77" s="6" t="s">
@@ -3735,8 +3586,8 @@
       <c r="I77" s="3"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="n">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -3751,7 +3602,7 @@
       <c r="E78" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F78" s="2">
         <v>15</v>
       </c>
       <c r="G78" s="6" t="s">
@@ -3763,8 +3614,8 @@
       <c r="I78" s="3"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2" t="n">
+    <row r="79" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -3779,7 +3630,7 @@
       <c r="E79" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F79" s="2">
         <v>20</v>
       </c>
       <c r="G79" s="6" t="s">
@@ -3791,8 +3642,8 @@
       <c r="I79" s="3"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="n">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -3807,7 +3658,7 @@
       <c r="E80" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F80" s="2">
         <v>20</v>
       </c>
       <c r="G80" s="6" t="s">
@@ -3819,8 +3670,8 @@
       <c r="I80" s="3"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="n">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -3835,7 +3686,7 @@
       <c r="E81" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="2">
         <v>20</v>
       </c>
       <c r="G81" s="6" t="s">
@@ -3847,8 +3698,8 @@
       <c r="I81" s="3"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="n">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -3863,7 +3714,7 @@
       <c r="E82" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="2">
         <v>25</v>
       </c>
       <c r="G82" s="6" t="s">
@@ -3875,8 +3726,8 @@
       <c r="I82" s="3"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="n">
+    <row r="83" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -3891,7 +3742,7 @@
       <c r="E83" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="F83" s="2">
         <v>15</v>
       </c>
       <c r="G83" s="6" t="s">
@@ -3903,8 +3754,8 @@
       <c r="I83" s="3"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="n">
+    <row r="84" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -3919,7 +3770,7 @@
       <c r="E84" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="F84" s="2">
         <v>20</v>
       </c>
       <c r="G84" s="6" t="s">
@@ -3931,8 +3782,8 @@
       <c r="I84" s="3"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="n">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -3947,7 +3798,7 @@
       <c r="E85" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="F85" s="2">
         <v>20</v>
       </c>
       <c r="G85" s="6" t="s">
@@ -3959,8 +3810,8 @@
       <c r="I85" s="3"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="n">
+    <row r="86" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -3975,7 +3826,7 @@
       <c r="E86" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F86" s="2">
         <v>25</v>
       </c>
       <c r="G86" s="6" t="s">
@@ -3987,8 +3838,8 @@
       <c r="I86" s="3"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="n">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -4003,7 +3854,7 @@
       <c r="E87" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="F87" s="2">
         <v>20</v>
       </c>
       <c r="G87" s="6" t="s">
@@ -4015,8 +3866,8 @@
       <c r="I87" s="3"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="n">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -4031,7 +3882,7 @@
       <c r="E88" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="F88" s="2">
         <v>25</v>
       </c>
       <c r="G88" s="6" t="s">
@@ -4043,8 +3894,8 @@
       <c r="I88" s="3"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="n">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -4059,7 +3910,7 @@
       <c r="E89" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="F89" s="2">
         <v>25</v>
       </c>
       <c r="G89" s="6" t="s">
@@ -4071,8 +3922,8 @@
       <c r="I89" s="3"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="n">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -4087,7 +3938,7 @@
       <c r="E90" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="F90" s="2">
         <v>25</v>
       </c>
       <c r="G90" s="6" t="s">
@@ -4099,8 +3950,8 @@
       <c r="I90" s="3"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="n">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
@@ -4115,7 +3966,7 @@
       <c r="E91" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="F91" s="2">
         <v>20</v>
       </c>
       <c r="G91" s="6" t="s">
@@ -4127,8 +3978,8 @@
       <c r="I91" s="3"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="n">
+    <row r="92" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
@@ -4143,7 +3994,7 @@
       <c r="E92" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="F92" s="2">
         <v>20</v>
       </c>
       <c r="G92" s="6" t="s">
@@ -4155,8 +4006,8 @@
       <c r="I92" s="3"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="n">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
@@ -4171,7 +4022,7 @@
       <c r="E93" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F93" s="2" t="n">
+      <c r="F93" s="2">
         <v>20</v>
       </c>
       <c r="G93" s="6" t="s">
@@ -4183,8 +4034,8 @@
       <c r="I93" s="3"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="n">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A94" s="2">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
@@ -4199,7 +4050,7 @@
       <c r="E94" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F94" s="2" t="n">
+      <c r="F94" s="2">
         <v>20</v>
       </c>
       <c r="G94" s="6" t="s">
@@ -4211,8 +4062,8 @@
       <c r="I94" s="3"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="n">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A95" s="2">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -4227,7 +4078,7 @@
       <c r="E95" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="2" t="n">
+      <c r="F95" s="2">
         <v>25</v>
       </c>
       <c r="G95" s="6" t="s">
@@ -4239,8 +4090,8 @@
       <c r="I95" s="3"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="n">
+    <row r="96" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A96" s="2">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -4255,7 +4106,7 @@
       <c r="E96" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F96" s="2" t="n">
+      <c r="F96" s="2">
         <v>20</v>
       </c>
       <c r="G96" s="6" t="s">
@@ -4267,8 +4118,8 @@
       <c r="I96" s="3"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="n">
+    <row r="97" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -4283,7 +4134,7 @@
       <c r="E97" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F97" s="2" t="n">
+      <c r="F97" s="2">
         <v>20</v>
       </c>
       <c r="G97" s="6" t="s">
@@ -4295,8 +4146,8 @@
       <c r="I97" s="3"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="n">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A98" s="2">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
@@ -4311,7 +4162,7 @@
       <c r="E98" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F98" s="2" t="n">
+      <c r="F98" s="2">
         <v>25</v>
       </c>
       <c r="G98" s="6" t="s">
@@ -4323,8 +4174,8 @@
       <c r="I98" s="3"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="n">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A99" s="2">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
@@ -4339,7 +4190,7 @@
       <c r="E99" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F99" s="2" t="n">
+      <c r="F99" s="2">
         <v>30</v>
       </c>
       <c r="G99" s="6" t="s">
@@ -4351,8 +4202,8 @@
       <c r="I99" s="3"/>
       <c r="J99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="n">
+    <row r="100" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A100" s="2">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
@@ -4367,7 +4218,7 @@
       <c r="E100" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F100" s="2" t="n">
+      <c r="F100" s="2">
         <v>15</v>
       </c>
       <c r="G100" s="6" t="s">
@@ -4379,8 +4230,8 @@
       <c r="I100" s="3"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="n">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
@@ -4395,7 +4246,7 @@
       <c r="E101" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F101" s="2" t="n">
+      <c r="F101" s="2">
         <v>20</v>
       </c>
       <c r="G101" s="6" t="s">
@@ -4407,8 +4258,8 @@
       <c r="I101" s="3"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="n">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A102" s="2">
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
@@ -4423,7 +4274,7 @@
       <c r="E102" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F102" s="2" t="n">
+      <c r="F102" s="2">
         <v>20</v>
       </c>
       <c r="G102" s="6" t="s">
@@ -4435,8 +4286,8 @@
       <c r="I102" s="3"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="n">
+    <row r="103" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A103" s="2">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
@@ -4451,7 +4302,7 @@
       <c r="E103" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F103" s="2" t="n">
+      <c r="F103" s="2">
         <v>25</v>
       </c>
       <c r="G103" s="6" t="s">
@@ -4463,8 +4314,8 @@
       <c r="I103" s="3"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="n">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A104" s="2">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
@@ -4479,7 +4330,7 @@
       <c r="E104" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F104" s="2" t="n">
+      <c r="F104" s="2">
         <v>20</v>
       </c>
       <c r="G104" s="6" t="s">
@@ -4491,8 +4342,8 @@
       <c r="I104" s="3"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="n">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A105" s="2">
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
@@ -4507,7 +4358,7 @@
       <c r="E105" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F105" s="2" t="n">
+      <c r="F105" s="2">
         <v>20</v>
       </c>
       <c r="G105" s="6" t="s">
@@ -4519,8 +4370,8 @@
       <c r="I105" s="3"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="n">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A106" s="2">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
@@ -4535,7 +4386,7 @@
       <c r="E106" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F106" s="2" t="n">
+      <c r="F106" s="2">
         <v>20</v>
       </c>
       <c r="G106" s="6" t="s">
@@ -4547,8 +4398,8 @@
       <c r="I106" s="3"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="n">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A107" s="2">
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
@@ -4563,7 +4414,7 @@
       <c r="E107" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F107" s="2" t="n">
+      <c r="F107" s="2">
         <v>20</v>
       </c>
       <c r="G107" s="6" t="s">
@@ -4575,8 +4426,8 @@
       <c r="I107" s="3"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="n">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A108" s="2">
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
@@ -4591,7 +4442,7 @@
       <c r="E108" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="2" t="n">
+      <c r="F108" s="2">
         <v>25</v>
       </c>
       <c r="G108" s="6" t="s">
@@ -4603,8 +4454,8 @@
       <c r="I108" s="3"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="n">
+    <row r="109" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A109" s="2">
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
@@ -4619,7 +4470,7 @@
       <c r="E109" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="2" t="n">
+      <c r="F109" s="2">
         <v>20</v>
       </c>
       <c r="G109" s="6" t="s">
@@ -4631,8 +4482,8 @@
       <c r="I109" s="3"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="n">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A110" s="2">
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
@@ -4647,7 +4498,7 @@
       <c r="E110" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F110" s="2" t="n">
+      <c r="F110" s="2">
         <v>15</v>
       </c>
       <c r="G110" s="6" t="s">
@@ -4659,8 +4510,8 @@
       <c r="I110" s="3"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="n">
+    <row r="111" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A111" s="2">
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
@@ -4675,7 +4526,7 @@
       <c r="E111" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F111" s="2" t="n">
+      <c r="F111" s="2">
         <v>20</v>
       </c>
       <c r="G111" s="6" t="s">
@@ -4687,8 +4538,8 @@
       <c r="I111" s="3"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="n">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A112" s="2">
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
@@ -4703,7 +4554,7 @@
       <c r="E112" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F112" s="2" t="n">
+      <c r="F112" s="2">
         <v>20</v>
       </c>
       <c r="G112" s="6" t="s">
@@ -4715,8 +4566,8 @@
       <c r="I112" s="3"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="n">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A113" s="2">
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
@@ -4731,7 +4582,7 @@
       <c r="E113" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F113" s="2" t="n">
+      <c r="F113" s="2">
         <v>25</v>
       </c>
       <c r="G113" s="6" t="s">
@@ -4743,8 +4594,8 @@
       <c r="I113" s="3"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="n">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A114" s="2">
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
@@ -4759,7 +4610,7 @@
       <c r="E114" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F114" s="2" t="n">
+      <c r="F114" s="2">
         <v>25</v>
       </c>
       <c r="G114" s="6" t="s">
@@ -4771,8 +4622,8 @@
       <c r="I114" s="3"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="n">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A115" s="2">
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
@@ -4787,7 +4638,7 @@
       <c r="E115" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F115" s="2" t="n">
+      <c r="F115" s="2">
         <v>25</v>
       </c>
       <c r="G115" s="6" t="s">
@@ -4799,8 +4650,8 @@
       <c r="I115" s="3"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="n">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A116" s="2">
         <v>115</v>
       </c>
       <c r="B116" s="3" t="s">
@@ -4815,7 +4666,7 @@
       <c r="E116" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F116" s="2" t="n">
+      <c r="F116" s="2">
         <v>25</v>
       </c>
       <c r="G116" s="6" t="s">
@@ -4827,8 +4678,8 @@
       <c r="I116" s="3"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2" t="n">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A117" s="2">
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
@@ -4843,7 +4694,7 @@
       <c r="E117" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F117" s="2" t="n">
+      <c r="F117" s="2">
         <v>30</v>
       </c>
       <c r="G117" s="6" t="s">
@@ -4855,8 +4706,8 @@
       <c r="I117" s="3"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="n">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A118" s="2">
         <v>117</v>
       </c>
       <c r="B118" s="3" t="s">
@@ -4871,7 +4722,7 @@
       <c r="E118" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F118" s="2" t="n">
+      <c r="F118" s="2">
         <v>20</v>
       </c>
       <c r="G118" s="6" t="s">
@@ -4883,8 +4734,8 @@
       <c r="I118" s="3"/>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="n">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A119" s="2">
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
@@ -4899,7 +4750,7 @@
       <c r="E119" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F119" s="2" t="n">
+      <c r="F119" s="2">
         <v>15</v>
       </c>
       <c r="G119" s="6" t="s">
@@ -4911,8 +4762,8 @@
       <c r="I119" s="3"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="n">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A120" s="2">
         <v>119</v>
       </c>
       <c r="B120" s="3" t="s">
@@ -4927,7 +4778,7 @@
       <c r="E120" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F120" s="2" t="n">
+      <c r="F120" s="2">
         <v>20</v>
       </c>
       <c r="G120" s="6" t="s">
@@ -4939,8 +4790,8 @@
       <c r="I120" s="3"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="n">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A121" s="2">
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
@@ -4955,7 +4806,7 @@
       <c r="E121" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F121" s="2" t="n">
+      <c r="F121" s="2">
         <v>20</v>
       </c>
       <c r="G121" s="6" t="s">
@@ -4967,8 +4818,8 @@
       <c r="I121" s="3"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="n">
+    <row r="122" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A122" s="2">
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
@@ -4983,7 +4834,7 @@
       <c r="E122" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F122" s="2" t="n">
+      <c r="F122" s="2">
         <v>25</v>
       </c>
       <c r="G122" s="6" t="s">
@@ -4995,8 +4846,8 @@
       <c r="I122" s="3"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="n">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A123" s="2">
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
@@ -5011,7 +4862,7 @@
       <c r="E123" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F123" s="2" t="n">
+      <c r="F123" s="2">
         <v>30</v>
       </c>
       <c r="G123" s="6" t="s">
@@ -5023,8 +4874,8 @@
       <c r="I123" s="3"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="n">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A124" s="2">
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
@@ -5039,7 +4890,7 @@
       <c r="E124" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F124" s="2" t="n">
+      <c r="F124" s="2">
         <v>20</v>
       </c>
       <c r="G124" s="6" t="s">
@@ -5051,8 +4902,8 @@
       <c r="I124" s="3"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="n">
+    <row r="125" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A125" s="2">
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
@@ -5067,7 +4918,7 @@
       <c r="E125" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F125" s="2" t="n">
+      <c r="F125" s="2">
         <v>20</v>
       </c>
       <c r="G125" s="6" t="s">
@@ -5079,8 +4930,8 @@
       <c r="I125" s="3"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="2" t="n">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A126" s="2">
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
@@ -5095,7 +4946,7 @@
       <c r="E126" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F126" s="2" t="n">
+      <c r="F126" s="2">
         <v>20</v>
       </c>
       <c r="G126" s="6" t="s">
@@ -5107,8 +4958,8 @@
       <c r="I126" s="3"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="n">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A127" s="2">
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
@@ -5123,7 +4974,7 @@
       <c r="E127" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F127" s="2" t="n">
+      <c r="F127" s="2">
         <v>20</v>
       </c>
       <c r="G127" s="6" t="s">
@@ -5135,8 +4986,8 @@
       <c r="I127" s="3"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="2" t="n">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A128" s="2">
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
@@ -5151,7 +5002,7 @@
       <c r="E128" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F128" s="2" t="n">
+      <c r="F128" s="2">
         <v>20</v>
       </c>
       <c r="G128" s="6" t="s">
@@ -5163,8 +5014,8 @@
       <c r="I128" s="3"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="n">
+    <row r="129" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A129" s="2">
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
@@ -5179,7 +5030,7 @@
       <c r="E129" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F129" s="2" t="n">
+      <c r="F129" s="2">
         <v>30</v>
       </c>
       <c r="G129" s="6" t="s">
@@ -5191,8 +5042,8 @@
       <c r="I129" s="3"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="n">
+    <row r="130" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A130" s="2">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
@@ -5207,7 +5058,7 @@
       <c r="E130" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F130" s="2" t="n">
+      <c r="F130" s="2">
         <v>25</v>
       </c>
       <c r="G130" s="6" t="s">
@@ -5219,8 +5070,8 @@
       <c r="I130" s="3"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="2" t="n">
+    <row r="131" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A131" s="2">
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
@@ -5235,7 +5086,7 @@
       <c r="E131" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F131" s="2" t="n">
+      <c r="F131" s="2">
         <v>30</v>
       </c>
       <c r="G131" s="6" t="s">
@@ -5248,277 +5099,268 @@
       <c r="J131" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H131" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H131" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId2" display="Open problem"/>
-    <hyperlink ref="E3" r:id="rId3" display="Open problem"/>
-    <hyperlink ref="E4" r:id="rId4" display="Open problem"/>
-    <hyperlink ref="E5" r:id="rId5" display="Open problem"/>
-    <hyperlink ref="E6" r:id="rId6" display="Open problem"/>
-    <hyperlink ref="E7" r:id="rId7" display="Open problem"/>
-    <hyperlink ref="E8" r:id="rId8" display="Open problem"/>
-    <hyperlink ref="E9" r:id="rId9" display="Open problem"/>
-    <hyperlink ref="E10" r:id="rId10" display="Open problem"/>
-    <hyperlink ref="E11" r:id="rId11" display="Open problem"/>
-    <hyperlink ref="E12" r:id="rId12" display="Open problem"/>
-    <hyperlink ref="E13" r:id="rId13" display="Open problem"/>
-    <hyperlink ref="E14" r:id="rId14" display="Open problem"/>
-    <hyperlink ref="E15" r:id="rId15" display="Open problem"/>
-    <hyperlink ref="E16" r:id="rId16" display="Open problem"/>
-    <hyperlink ref="E17" r:id="rId17" display="Open problem"/>
-    <hyperlink ref="E18" r:id="rId18" display="Open problem"/>
-    <hyperlink ref="E19" r:id="rId19" display="Open problem"/>
-    <hyperlink ref="E20" r:id="rId20" display="Open problem"/>
-    <hyperlink ref="E21" r:id="rId21" display="Open problem"/>
-    <hyperlink ref="E22" r:id="rId22" display="Open problem"/>
-    <hyperlink ref="E23" r:id="rId23" display="Open problem"/>
-    <hyperlink ref="E24" r:id="rId24" display="Open problem"/>
-    <hyperlink ref="E25" r:id="rId25" display="Open problem"/>
-    <hyperlink ref="E26" r:id="rId26" display="Open problem"/>
-    <hyperlink ref="E27" r:id="rId27" display="Open problem"/>
-    <hyperlink ref="E28" r:id="rId28" display="Open problem"/>
-    <hyperlink ref="E29" r:id="rId29" display="Open problem"/>
-    <hyperlink ref="E30" r:id="rId30" display="Open problem"/>
-    <hyperlink ref="E31" r:id="rId31" display="Open problem"/>
-    <hyperlink ref="E32" r:id="rId32" display="Open problem"/>
-    <hyperlink ref="E33" r:id="rId33" display="Open problem"/>
-    <hyperlink ref="E34" r:id="rId34" display="Open problem"/>
-    <hyperlink ref="E35" r:id="rId35" display="Open problem"/>
-    <hyperlink ref="E36" r:id="rId36" display="Open problem"/>
-    <hyperlink ref="E37" r:id="rId37" display="Open problem"/>
-    <hyperlink ref="E38" r:id="rId38" display="Open problem"/>
-    <hyperlink ref="E39" r:id="rId39" display="Open problem"/>
-    <hyperlink ref="E40" r:id="rId40" display="Open problem"/>
-    <hyperlink ref="E41" r:id="rId41" display="Open problem"/>
-    <hyperlink ref="E42" r:id="rId42" display="Open problem"/>
-    <hyperlink ref="E43" r:id="rId43" display="Open problem"/>
-    <hyperlink ref="E44" r:id="rId44" display="Open problem"/>
-    <hyperlink ref="E45" r:id="rId45" display="Open problem"/>
-    <hyperlink ref="E46" r:id="rId46" display="Open problem"/>
-    <hyperlink ref="E47" r:id="rId47" display="Open problem"/>
-    <hyperlink ref="E48" r:id="rId48" display="Open problem"/>
-    <hyperlink ref="E49" r:id="rId49" display="Open problem"/>
-    <hyperlink ref="E50" r:id="rId50" display="Open problem"/>
-    <hyperlink ref="E51" r:id="rId51" display="Open problem"/>
-    <hyperlink ref="E52" r:id="rId52" display="Open problem"/>
-    <hyperlink ref="E53" r:id="rId53" display="Open problem"/>
-    <hyperlink ref="E54" r:id="rId54" display="Open problem"/>
-    <hyperlink ref="E55" r:id="rId55" display="Open problem"/>
-    <hyperlink ref="E56" r:id="rId56" display="Open problem"/>
-    <hyperlink ref="E57" r:id="rId57" display="Open problem"/>
-    <hyperlink ref="E58" r:id="rId58" display="Open problem"/>
-    <hyperlink ref="E59" r:id="rId59" display="Open problem"/>
-    <hyperlink ref="E60" r:id="rId60" display="Open problem"/>
-    <hyperlink ref="E61" r:id="rId61" display="Open problem"/>
-    <hyperlink ref="E62" r:id="rId62" display="Open problem"/>
-    <hyperlink ref="E63" r:id="rId63" display="Open problem"/>
-    <hyperlink ref="E64" r:id="rId64" display="Open problem"/>
-    <hyperlink ref="E65" r:id="rId65" display="Open problem"/>
-    <hyperlink ref="E66" r:id="rId66" display="Open problem"/>
-    <hyperlink ref="E67" r:id="rId67" display="Open problem"/>
-    <hyperlink ref="E68" r:id="rId68" display="Open problem"/>
-    <hyperlink ref="E69" r:id="rId69" display="Open problem"/>
-    <hyperlink ref="E70" r:id="rId70" display="Open problem"/>
-    <hyperlink ref="E71" r:id="rId71" display="Open problem"/>
-    <hyperlink ref="E72" r:id="rId72" display="Open problem"/>
-    <hyperlink ref="E73" r:id="rId73" display="Open problem"/>
-    <hyperlink ref="E74" r:id="rId74" display="Open problem"/>
-    <hyperlink ref="E75" r:id="rId75" display="Open problem"/>
-    <hyperlink ref="E76" r:id="rId76" display="Open problem"/>
-    <hyperlink ref="E77" r:id="rId77" display="Open problem"/>
-    <hyperlink ref="E78" r:id="rId78" display="Open problem"/>
-    <hyperlink ref="E79" r:id="rId79" display="Open problem"/>
-    <hyperlink ref="E80" r:id="rId80" display="Open problem"/>
-    <hyperlink ref="E81" r:id="rId81" display="Open problem"/>
-    <hyperlink ref="E82" r:id="rId82" display="Open problem"/>
-    <hyperlink ref="E83" r:id="rId83" display="Open problem"/>
-    <hyperlink ref="E84" r:id="rId84" display="Open problem"/>
-    <hyperlink ref="E85" r:id="rId85" display="Open problem"/>
-    <hyperlink ref="E86" r:id="rId86" display="Open problem"/>
-    <hyperlink ref="E87" r:id="rId87" display="Open problem"/>
-    <hyperlink ref="E88" r:id="rId88" display="Open problem"/>
-    <hyperlink ref="E89" r:id="rId89" display="Open problem"/>
-    <hyperlink ref="E90" r:id="rId90" display="Open problem"/>
-    <hyperlink ref="E91" r:id="rId91" display="Open problem"/>
-    <hyperlink ref="E92" r:id="rId92" display="Open problem"/>
-    <hyperlink ref="E93" r:id="rId93" display="Open problem"/>
-    <hyperlink ref="E94" r:id="rId94" display="Open problem"/>
-    <hyperlink ref="E95" r:id="rId95" display="Open problem"/>
-    <hyperlink ref="E96" r:id="rId96" display="Open problem"/>
-    <hyperlink ref="E97" r:id="rId97" display="Open problem"/>
-    <hyperlink ref="E98" r:id="rId98" display="Open problem"/>
-    <hyperlink ref="E99" r:id="rId99" display="Open problem"/>
-    <hyperlink ref="E100" r:id="rId100" display="Open problem"/>
-    <hyperlink ref="E101" r:id="rId101" display="Open problem"/>
-    <hyperlink ref="E102" r:id="rId102" display="Open problem"/>
-    <hyperlink ref="E103" r:id="rId103" display="Open problem"/>
-    <hyperlink ref="E104" r:id="rId104" display="Open problem"/>
-    <hyperlink ref="E105" r:id="rId105" display="Open problem"/>
-    <hyperlink ref="E106" r:id="rId106" display="Open problem"/>
-    <hyperlink ref="E107" r:id="rId107" display="Open problem"/>
-    <hyperlink ref="E108" r:id="rId108" display="Open problem"/>
-    <hyperlink ref="E109" r:id="rId109" display="Open problem"/>
-    <hyperlink ref="E110" r:id="rId110" display="Open problem"/>
-    <hyperlink ref="E111" r:id="rId111" display="Open problem"/>
-    <hyperlink ref="E112" r:id="rId112" display="Open problem"/>
-    <hyperlink ref="E113" r:id="rId113" display="Open problem"/>
-    <hyperlink ref="E114" r:id="rId114" display="Open problem"/>
-    <hyperlink ref="E115" r:id="rId115" display="Open problem"/>
-    <hyperlink ref="E116" r:id="rId116" display="Open problem"/>
-    <hyperlink ref="E117" r:id="rId117" display="Open problem"/>
-    <hyperlink ref="E118" r:id="rId118" display="Open problem"/>
-    <hyperlink ref="E119" r:id="rId119" display="Open problem"/>
-    <hyperlink ref="E120" r:id="rId120" display="Open problem"/>
-    <hyperlink ref="E121" r:id="rId121" display="Open problem"/>
-    <hyperlink ref="E122" r:id="rId122" display="Open problem"/>
-    <hyperlink ref="E123" r:id="rId123" display="Open problem"/>
-    <hyperlink ref="E124" r:id="rId124" display="Open problem"/>
-    <hyperlink ref="E125" r:id="rId125" display="Open problem"/>
-    <hyperlink ref="E126" r:id="rId126" display="Open problem"/>
-    <hyperlink ref="E127" r:id="rId127" display="Open problem"/>
-    <hyperlink ref="E128" r:id="rId128" display="Open problem"/>
-    <hyperlink ref="E129" r:id="rId129" display="Open problem"/>
-    <hyperlink ref="E130" r:id="rId130" display="Open problem"/>
-    <hyperlink ref="E131" r:id="rId131" display="Open problem"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="E12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="E14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="E16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="E18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="E19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="E20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="E21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="E22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="E24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="E25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="E26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="E27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="E28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="E29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="E30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="E31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="E32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="E33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="E34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="E35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="E36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="E37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="E38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="E39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="E40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="E41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="E42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="E43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="E44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="E45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="E46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="E47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="E48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="E49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="E50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="E51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="E52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="E53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="E54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="E55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="E56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="E57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="E58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="E59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="E60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="E61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="E62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="E63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="E64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="E65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="E66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="E67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="E68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="E69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="E70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="E71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="E72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="E73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="E74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="E75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="E76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="E77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="E78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="E79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="E80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="E81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="E82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="E83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="E84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="E85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="E86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="E87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="E88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="E89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="E90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="E91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="E92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="E93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="E94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="E95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="E96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="E97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="E98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="E99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="E100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="E101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="E102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="E103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="E104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="E105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="E106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="E107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="E108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="E109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="E110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="E111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="E112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="E113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="E114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="E115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="E116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="E117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="E118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="E119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="E120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="E121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="E122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="E123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="E124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="E125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="E126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="E127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="E128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="E129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="E130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="E131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId132"/>
-  <legacyDrawing r:id="rId133"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId131"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="17.649999999999999" x14ac:dyDescent="0.5">
+      <c r="A1" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="10" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D2" s="12" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D2" s="11" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B3" s="13" t="n">
-        <f aca="false">COUNTA('130-Day Plan'!A2:A131)</f>
+      <c r="B3" s="12">
+        <f>COUNTA('130-Day Plan'!A2:A131)</f>
         <v>130</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="B4" s="13" t="n">
-        <f aca="false">COUNTIF('130-Day Plan'!H2:H131,"Done")</f>
+      <c r="B4" s="12">
+        <f>COUNTIF('130-Day Plan'!H2:H131,"Done")</f>
         <v>0</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B5" s="13" t="n">
-        <f aca="false">COUNTIF('130-Day Plan'!H2:H131,"In Progress")</f>
+      <c r="B5" s="12">
+        <f>COUNTIF('130-Day Plan'!H2:H131,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="13" t="n">
-        <f aca="false">COUNTIF('130-Day Plan'!H2:H131,"Not Started")</f>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="12">
+        <f>COUNTIF('130-Day Plan'!H2:H131,"Not Started")</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="B7" s="13" t="n">
-        <f aca="false">COUNTIF('130-Day Plan'!H2:H131,"Skipped")</f>
+      <c r="B7" s="12">
+        <f>COUNTIF('130-Day Plan'!H2:H131,"Skipped")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B8" s="15" t="n">
-        <f aca="false">B4/B3</f>
+      <c r="B8" s="14">
+        <f>B4/B3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="10" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="13" t="n">
-        <f aca="false">COUNTIF('130-Day Plan'!D2:D131,"Easy")</f>
+      <c r="B12" s="12">
+        <f>COUNTIF('130-Day Plan'!D2:D131,"Easy")</f>
         <v>44</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="13" t="n">
-        <f aca="false">COUNTIF('130-Day Plan'!D2:D131,"Medium")</f>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="12">
+        <f>COUNTIF('130-Day Plan'!D2:D131,"Medium")</f>
         <v>81</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="13" t="n">
-        <f aca="false">COUNTIF('130-Day Plan'!D2:D131,"Hard")</f>
+      <c r="B14" s="12">
+        <f>COUNTIF('130-Day Plan'!D2:D131,"Hard")</f>
         <v>5</v>
       </c>
     </row>
@@ -5526,12 +5368,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
+++ b/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD35782F-1963-4661-A23B-B4662ED8A6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE33BC0-3FC6-4564-A31F-3E3431B5FC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1649,7 +1649,7 @@
         <v>28</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="7"/>
@@ -1677,7 +1677,7 @@
         <v>30</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="7"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="B6" s="12">
         <f>COUNTIF('130-Day Plan'!H2:H131,"Not Started")</f>
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">

--- a/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
+++ b/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE33BC0-3FC6-4564-A31F-3E3431B5FC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBCFAC5-C564-4D27-8B14-611638411F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="304">
   <si>
     <t>Day</t>
   </si>
@@ -970,6 +970,9 @@
   </si>
   <si>
     <t>completed</t>
+  </si>
+  <si>
+    <t>completed(not)</t>
   </si>
 </sst>
 </file>
@@ -1705,7 +1708,7 @@
         <v>32</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>15</v>
+        <v>303</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="7"/>
@@ -5311,7 +5314,7 @@
       </c>
       <c r="B6" s="12">
         <f>COUNTIF('130-Day Plan'!H2:H131,"Not Started")</f>
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">

--- a/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
+++ b/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBCFAC5-C564-4D27-8B14-611638411F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89501D03-1FDF-4C21-8EB1-59F56B47B372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'130-Day Plan'!$A$1:$J$131</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1414,6 +1415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J131"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1545,7 +1547,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1736,7 +1738,7 @@
         <v>34</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>15</v>
+        <v>303</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="7"/>
@@ -1797,7 +1799,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1881,7 +1883,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1909,7 +1911,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1937,7 +1939,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1993,7 +1995,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2021,7 +2023,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2049,7 +2051,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2077,7 +2079,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2105,7 +2107,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2133,7 +2135,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2161,7 +2163,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2217,7 +2219,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2245,7 +2247,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2273,7 +2275,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2301,7 +2303,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2497,7 +2499,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2525,7 +2527,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2581,7 +2583,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2609,7 +2611,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2805,7 +2807,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2833,7 +2835,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2861,7 +2863,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2889,7 +2891,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2917,7 +2919,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3001,7 +3003,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3029,7 +3031,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3085,7 +3087,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3113,7 +3115,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3225,7 +3227,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -3253,7 +3255,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3281,7 +3283,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -3309,7 +3311,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -3337,7 +3339,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3477,7 +3479,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3589,7 +3591,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3617,7 +3619,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3645,7 +3647,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3673,7 +3675,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3701,7 +3703,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -3757,7 +3759,7 @@
       <c r="I83" s="3"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3785,7 +3787,7 @@
       <c r="I84" s="3"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3813,7 +3815,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3841,7 +3843,7 @@
       <c r="I86" s="3"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3869,7 +3871,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3897,7 +3899,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3925,7 +3927,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3953,7 +3955,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3981,7 +3983,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4009,7 +4011,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -4037,7 +4039,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4065,7 +4067,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -4093,7 +4095,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4121,7 +4123,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -4149,7 +4151,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -4177,7 +4179,7 @@
       <c r="I98" s="3"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -4233,7 +4235,7 @@
       <c r="I100" s="3"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -4261,7 +4263,7 @@
       <c r="I101" s="3"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -4289,7 +4291,7 @@
       <c r="I102" s="3"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -4317,7 +4319,7 @@
       <c r="I103" s="3"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -4345,7 +4347,7 @@
       <c r="I104" s="3"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -4373,7 +4375,7 @@
       <c r="I105" s="3"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -4401,7 +4403,7 @@
       <c r="I106" s="3"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -4429,7 +4431,7 @@
       <c r="I107" s="3"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -4457,7 +4459,7 @@
       <c r="I108" s="3"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -4485,7 +4487,7 @@
       <c r="I109" s="3"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -4513,7 +4515,7 @@
       <c r="I110" s="3"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -4541,7 +4543,7 @@
       <c r="I111" s="3"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -4569,7 +4571,7 @@
       <c r="I112" s="3"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -4597,7 +4599,7 @@
       <c r="I113" s="3"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -4625,7 +4627,7 @@
       <c r="I114" s="3"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -4653,7 +4655,7 @@
       <c r="I115" s="3"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -4681,7 +4683,7 @@
       <c r="I116" s="3"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -4709,7 +4711,7 @@
       <c r="I117" s="3"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -4765,7 +4767,7 @@
       <c r="I119" s="3"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -4793,7 +4795,7 @@
       <c r="I120" s="3"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -4821,7 +4823,7 @@
       <c r="I121" s="3"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -4849,7 +4851,7 @@
       <c r="I122" s="3"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -4877,7 +4879,7 @@
       <c r="I123" s="3"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -4905,7 +4907,7 @@
       <c r="I124" s="3"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -4933,7 +4935,7 @@
       <c r="I125" s="3"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -4961,7 +4963,7 @@
       <c r="I126" s="3"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -4989,7 +4991,7 @@
       <c r="I127" s="3"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -5017,7 +5019,7 @@
       <c r="I128" s="3"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -5045,7 +5047,7 @@
       <c r="I129" s="3"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -5073,7 +5075,7 @@
       <c r="I130" s="3"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -5102,7 +5104,13 @@
       <c r="J131" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Easy"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H2:H131" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Done,Skipped"</formula1>
@@ -5314,7 +5322,7 @@
       </c>
       <c r="B6" s="12">
         <f>COUNTIF('130-Day Plan'!H2:H131,"Not Started")</f>
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">

--- a/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
+++ b/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89501D03-1FDF-4C21-8EB1-59F56B47B372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B982B9D-4C91-497D-B8DB-7E29F7FB531E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'130-Day Plan'!$A$1:$J$131</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1415,7 +1414,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J131"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1547,7 +1545,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1766,7 +1764,7 @@
         <v>37</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="7"/>
@@ -1794,12 +1792,12 @@
         <v>39</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1883,7 +1881,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1911,7 +1909,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1939,7 +1937,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1995,7 +1993,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2023,7 +2021,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2051,7 +2049,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2079,7 +2077,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2107,7 +2105,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2135,7 +2133,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2163,7 +2161,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2219,7 +2217,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2247,7 +2245,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2275,7 +2273,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2303,7 +2301,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2499,7 +2497,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2527,7 +2525,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2583,7 +2581,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2611,7 +2609,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2807,7 +2805,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2835,7 +2833,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2863,7 +2861,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2891,7 +2889,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2919,7 +2917,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3003,7 +3001,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3031,7 +3029,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3087,7 +3085,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3115,7 +3113,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3227,7 +3225,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -3255,7 +3253,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3283,7 +3281,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -3311,7 +3309,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -3339,7 +3337,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3479,7 +3477,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3591,7 +3589,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3619,7 +3617,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3647,7 +3645,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3675,7 +3673,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3703,7 +3701,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -3759,7 +3757,7 @@
       <c r="I83" s="3"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3787,7 +3785,7 @@
       <c r="I84" s="3"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3815,7 +3813,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3843,7 +3841,7 @@
       <c r="I86" s="3"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3871,7 +3869,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3899,7 +3897,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3927,7 +3925,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3955,7 +3953,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3983,7 +3981,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4011,7 +4009,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -4039,7 +4037,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4067,7 +4065,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -4095,7 +4093,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4123,7 +4121,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -4151,7 +4149,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -4179,7 +4177,7 @@
       <c r="I98" s="3"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -4235,7 +4233,7 @@
       <c r="I100" s="3"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -4263,7 +4261,7 @@
       <c r="I101" s="3"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -4291,7 +4289,7 @@
       <c r="I102" s="3"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -4319,7 +4317,7 @@
       <c r="I103" s="3"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -4347,7 +4345,7 @@
       <c r="I104" s="3"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -4375,7 +4373,7 @@
       <c r="I105" s="3"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -4403,7 +4401,7 @@
       <c r="I106" s="3"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -4431,7 +4429,7 @@
       <c r="I107" s="3"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -4459,7 +4457,7 @@
       <c r="I108" s="3"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -4487,7 +4485,7 @@
       <c r="I109" s="3"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -4515,7 +4513,7 @@
       <c r="I110" s="3"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -4543,7 +4541,7 @@
       <c r="I111" s="3"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -4571,7 +4569,7 @@
       <c r="I112" s="3"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -4599,7 +4597,7 @@
       <c r="I113" s="3"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -4627,7 +4625,7 @@
       <c r="I114" s="3"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -4655,7 +4653,7 @@
       <c r="I115" s="3"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -4683,7 +4681,7 @@
       <c r="I116" s="3"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -4711,7 +4709,7 @@
       <c r="I117" s="3"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -4767,7 +4765,7 @@
       <c r="I119" s="3"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -4795,7 +4793,7 @@
       <c r="I120" s="3"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -4823,7 +4821,7 @@
       <c r="I121" s="3"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -4851,7 +4849,7 @@
       <c r="I122" s="3"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -4879,7 +4877,7 @@
       <c r="I123" s="3"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -4907,7 +4905,7 @@
       <c r="I124" s="3"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -4935,7 +4933,7 @@
       <c r="I125" s="3"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -4963,7 +4961,7 @@
       <c r="I126" s="3"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -4991,7 +4989,7 @@
       <c r="I127" s="3"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -5019,7 +5017,7 @@
       <c r="I128" s="3"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -5047,7 +5045,7 @@
       <c r="I129" s="3"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -5075,7 +5073,7 @@
       <c r="I130" s="3"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -5104,13 +5102,7 @@
       <c r="J131" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Easy"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H2:H131" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Done,Skipped"</formula1>
@@ -5118,136 +5110,136 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="E12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="E16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="E18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="E19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="E20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="E21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="E22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="E23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="E24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="E25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="E26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="E27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="E28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="E29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="E30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="E31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="E32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="E33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="E34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="E35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="E36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="E37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="E38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="E39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="E40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="E41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="E42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="E43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="E44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="E45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="E46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="E47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="E48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="E49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="E50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="E51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="E52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="E53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="E54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="E55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="E56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="E57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="E58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="E59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="E60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="E61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="E62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="E63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="E64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="E65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="E66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="E67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="E68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="E69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="E70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="E71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="E72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="E73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="E74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="E75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="E76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="E77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="E78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="E79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="E80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="E81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="E82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="E83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="E84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="E85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="E86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="E87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="E88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="E89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="E90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="E91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="E92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="E93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="E94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="E95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="E96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="E97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="E98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="E99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="E100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="E101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="E102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="E103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="E104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="E105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="E106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="E107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="E108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="E109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="E110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="E111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="E112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="E113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="E114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="E115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="E116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="E117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="E118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="E119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="E120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="E121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="E122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="E123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="E124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="E125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="E126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="E127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="E128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="E129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="E130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="E131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="E12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="E14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E17" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="E18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="E19" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="E21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="E22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="E24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="E25" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="E26" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="E27" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="E29" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="E30" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="E31" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="E32" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="E39" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="E40" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="E42" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="E43" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="E50" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="E51" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="E52" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="E53" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="E54" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="E57" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="E58" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="E60" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="E61" r:id="rId37" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="E65" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="E66" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="E67" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="E68" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="E69" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="E74" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="E78" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="E79" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="E80" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="E81" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="E82" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="E84" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="E85" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="E86" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="E87" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="E88" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="E89" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="E90" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="E91" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="E92" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="E93" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="E94" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="E95" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="E96" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="E97" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="E98" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="E99" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="E101" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="E102" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="E103" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="E104" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="E105" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="E106" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="E107" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="E108" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="E109" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="E110" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="E111" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="E112" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="E113" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="E114" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="E115" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="E116" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="E117" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="E118" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="E120" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="E121" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="E122" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="E123" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="E124" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="E125" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="E126" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="E127" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="E128" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="E129" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="E130" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="E131" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="E119" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="E100" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="E83" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="E77" r:id="rId98" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="E76" r:id="rId99" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="E75" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="E73" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="E72" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="E71" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="E70" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="E64" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="E63" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="E62" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="E59" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="E56" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="E55" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="E49" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="E48" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="E47" r:id="rId113" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="E46" r:id="rId114" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="E45" r:id="rId115" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="E44" r:id="rId116" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="E41" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="E38" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="E37" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="E36" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="E35" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="E34" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="E33" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="E28" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="E20" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="E16" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E15" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="E4" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E3" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E2" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5322,7 +5314,7 @@
       </c>
       <c r="B6" s="12">
         <f>COUNTIF('130-Day Plan'!H2:H131,"Not Started")</f>
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">

--- a/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
+++ b/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B982B9D-4C91-497D-B8DB-7E29F7FB531E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A368371-1742-4245-9943-C5D902F52B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1820,7 +1820,7 @@
         <v>41</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="7"/>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="B6" s="12">
         <f>COUNTIF('130-Day Plan'!H2:H131,"Not Started")</f>
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">

--- a/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
+++ b/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A368371-1742-4245-9943-C5D902F52B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E93E71E-2D96-4BC8-913D-D374D6061907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1414,6 +1414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J131"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1461,7 +1462,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1489,7 +1490,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1517,7 +1518,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1545,7 +1546,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1573,7 +1574,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1601,7 +1602,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1629,7 +1630,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1657,7 +1658,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1685,7 +1686,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1713,7 +1714,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1741,7 +1742,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1769,7 +1770,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1797,7 +1798,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1825,7 +1826,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1848,12 +1849,12 @@
         <v>43</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1876,12 +1877,12 @@
         <v>45</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1904,12 +1905,12 @@
         <v>47</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>15</v>
+        <v>303</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1937,7 +1938,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1993,7 +1994,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2021,7 +2022,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2049,7 +2050,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2077,7 +2078,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2105,7 +2106,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2133,7 +2134,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2161,7 +2162,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2217,7 +2218,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2245,7 +2246,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2273,7 +2274,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2301,7 +2302,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2497,7 +2498,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2525,7 +2526,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2581,7 +2582,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2609,7 +2610,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2805,7 +2806,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2833,7 +2834,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2861,7 +2862,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2889,7 +2890,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2917,7 +2918,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3001,7 +3002,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3029,7 +3030,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3085,7 +3086,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3113,7 +3114,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3225,7 +3226,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -3253,7 +3254,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3281,7 +3282,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -3309,7 +3310,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -3337,7 +3338,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3477,7 +3478,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3589,7 +3590,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3617,7 +3618,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3645,7 +3646,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3673,7 +3674,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3701,7 +3702,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -3757,7 +3758,7 @@
       <c r="I83" s="3"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3785,7 +3786,7 @@
       <c r="I84" s="3"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3813,7 +3814,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3841,7 +3842,7 @@
       <c r="I86" s="3"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3869,7 +3870,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3897,7 +3898,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3925,7 +3926,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3953,7 +3954,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3981,7 +3982,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4009,7 +4010,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -4037,7 +4038,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4065,7 +4066,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -4093,7 +4094,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4121,7 +4122,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -4149,7 +4150,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -4177,7 +4178,7 @@
       <c r="I98" s="3"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -4233,7 +4234,7 @@
       <c r="I100" s="3"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -4261,7 +4262,7 @@
       <c r="I101" s="3"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -4289,7 +4290,7 @@
       <c r="I102" s="3"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -4317,7 +4318,7 @@
       <c r="I103" s="3"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -4345,7 +4346,7 @@
       <c r="I104" s="3"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -4373,7 +4374,7 @@
       <c r="I105" s="3"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -4401,7 +4402,7 @@
       <c r="I106" s="3"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -4429,7 +4430,7 @@
       <c r="I107" s="3"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -4457,7 +4458,7 @@
       <c r="I108" s="3"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -4485,7 +4486,7 @@
       <c r="I109" s="3"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -4513,7 +4514,7 @@
       <c r="I110" s="3"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -4541,7 +4542,7 @@
       <c r="I111" s="3"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -4569,7 +4570,7 @@
       <c r="I112" s="3"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -4597,7 +4598,7 @@
       <c r="I113" s="3"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -4625,7 +4626,7 @@
       <c r="I114" s="3"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -4653,7 +4654,7 @@
       <c r="I115" s="3"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -4681,7 +4682,7 @@
       <c r="I116" s="3"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -4709,7 +4710,7 @@
       <c r="I117" s="3"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -4765,7 +4766,7 @@
       <c r="I119" s="3"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -4793,7 +4794,7 @@
       <c r="I120" s="3"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -4821,7 +4822,7 @@
       <c r="I121" s="3"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -4849,7 +4850,7 @@
       <c r="I122" s="3"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -4877,7 +4878,7 @@
       <c r="I123" s="3"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -4905,7 +4906,7 @@
       <c r="I124" s="3"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -4933,7 +4934,7 @@
       <c r="I125" s="3"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -4961,7 +4962,7 @@
       <c r="I126" s="3"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -4989,7 +4990,7 @@
       <c r="I127" s="3"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -5017,7 +5018,7 @@
       <c r="I128" s="3"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -5045,7 +5046,7 @@
       <c r="I129" s="3"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -5073,7 +5074,7 @@
       <c r="I130" s="3"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -5102,7 +5103,18 @@
       <c r="J131" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Easy"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Not Started"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H2:H131" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Done,Skipped"</formula1>
@@ -5314,7 +5326,7 @@
       </c>
       <c r="B6" s="12">
         <f>COUNTIF('130-Day Plan'!H2:H131,"Not Started")</f>
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">

--- a/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
+++ b/3aed9d04-2385-4fdd-b403-316e5db325c7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E93E71E-2D96-4BC8-913D-D374D6061907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3513D467-9EA2-44D4-9D1C-91043BB005B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="21795" windowHeight="11625" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="130-Day Plan" sheetId="1" r:id="rId1"/>
@@ -1546,7 +1546,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1686,7 +1686,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1714,7 +1714,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1882,7 +1882,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1910,7 +1910,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1938,7 +1938,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1994,7 +1994,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2022,7 +2022,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2050,7 +2050,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2078,7 +2078,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2106,7 +2106,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2134,7 +2134,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2162,7 +2162,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2218,7 +2218,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2246,7 +2246,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2498,7 +2498,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2526,7 +2526,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2582,7 +2582,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2610,7 +2610,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2806,7 +2806,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2834,7 +2834,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2862,7 +2862,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2890,7 +2890,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2918,7 +2918,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3002,7 +3002,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3030,7 +3030,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3086,7 +3086,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3114,7 +3114,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3226,7 +3226,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -3254,7 +3254,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3282,7 +3282,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -3310,7 +3310,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -3338,7 +3338,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3478,7 +3478,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3590,7 +3590,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3618,7 +3618,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3702,7 +3702,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -3758,7 +3758,7 @@
       <c r="I83" s="3"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3786,7 +3786,7 @@
       <c r="I84" s="3"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3842,7 +3842,7 @@
       <c r="I86" s="3"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3870,7 +3870,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3898,7 +3898,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3926,7 +3926,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3954,7 +3954,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3982,7 +3982,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4010,7 +4010,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4066,7 +4066,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -4094,7 +4094,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4122,7 +4122,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -4150,7 +4150,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -4178,7 +4178,7 @@
       <c r="I98" s="3"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -4234,7 +4234,7 @@
       <c r="I100" s="3"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -4262,7 +4262,7 @@
       <c r="I101" s="3"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="I102" s="3"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -4318,7 +4318,7 @@
       <c r="I103" s="3"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -4346,7 +4346,7 @@
       <c r="I104" s="3"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -4374,7 +4374,7 @@
       <c r="I105" s="3"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -4402,7 +4402,7 @@
       <c r="I106" s="3"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -4430,7 +4430,7 @@
       <c r="I107" s="3"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -4458,7 +4458,7 @@
       <c r="I108" s="3"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -4486,7 +4486,7 @@
       <c r="I109" s="3"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="I110" s="3"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -4542,7 +4542,7 @@
       <c r="I111" s="3"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -4570,7 +4570,7 @@
       <c r="I112" s="3"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -4598,7 +4598,7 @@
       <c r="I113" s="3"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -4626,7 +4626,7 @@
       <c r="I114" s="3"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -4654,7 +4654,7 @@
       <c r="I115" s="3"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -4682,7 +4682,7 @@
       <c r="I116" s="3"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -4710,7 +4710,7 @@
       <c r="I117" s="3"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -4766,7 +4766,7 @@
       <c r="I119" s="3"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -4794,7 +4794,7 @@
       <c r="I120" s="3"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -4822,7 +4822,7 @@
       <c r="I121" s="3"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -4850,7 +4850,7 @@
       <c r="I122" s="3"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -4878,7 +4878,7 @@
       <c r="I123" s="3"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -4906,7 +4906,7 @@
       <c r="I124" s="3"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -4934,7 +4934,7 @@
       <c r="I125" s="3"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -4962,7 +4962,7 @@
       <c r="I126" s="3"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -4990,7 +4990,7 @@
       <c r="I127" s="3"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -5018,7 +5018,7 @@
       <c r="I128" s="3"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -5046,7 +5046,7 @@
       <c r="I129" s="3"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -5074,7 +5074,7 @@
       <c r="I130" s="3"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" ht="27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -5104,13 +5104,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Easy"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="7">
       <filters>
+        <filter val="completed(not)"/>
         <filter val="Not Started"/>
       </filters>
     </filterColumn>
